--- a/data/Unidad_de_Negocio.xlsx
+++ b/data/Unidad_de_Negocio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officedepotcommx-my.sharepoint.com/personal/iboyr_brian_officedepot_com_gt/Documents/Reabasto/TiendasTutoras/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Reabasto6\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{1B2DC175-2F08-4493-9B1D-FEAD503474FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62F33E7E-2F0D-4E63-BE06-4C1CCBFD0CE7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EDCD10-4FEF-414C-8C5E-0DF1FAD9AFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{F2E579F4-3600-454E-9F00-3B96FEDCB91B}"/>
   </bookViews>
@@ -62,12 +62,6 @@
     <t>OD | GT | 601 TIENDA MAJADAS</t>
   </si>
   <si>
-    <t>OD | GT | 602 TIENDA PRÓCERES</t>
-  </si>
-  <si>
-    <t>OD | GT | 603 TIENDA PLAZUELA ESPAÑA EXPRESS</t>
-  </si>
-  <si>
     <t>OD | GT | 605 TIENDA CARRETERA A EL SALVADOR</t>
   </si>
   <si>
@@ -77,15 +71,9 @@
     <t>OD | GT | 607 TIENDA PORTALES ZONA 17</t>
   </si>
   <si>
-    <t>OD | GT | 608 TIENDA SAN CRISTÓBAL</t>
-  </si>
-  <si>
     <t>OD | GT | 609 TIENDA ANTIGUA GUATEMALA EXPRESS</t>
   </si>
   <si>
-    <t>OD | GT | 610 TIENDA CAYALÁ</t>
-  </si>
-  <si>
     <t>OD | SA | 641 TIENDA LOS HEROES</t>
   </si>
   <si>
@@ -183,6 +171,18 @@
   </si>
   <si>
     <t>OD | GT | 610 TIENDA CAYALÃ</t>
+  </si>
+  <si>
+    <t>OD | GT | 602 TIENDA PROCERES</t>
+  </si>
+  <si>
+    <t>OD | GT | 603 TIENDA PLAZUELA ESPANA EXPRESS</t>
+  </si>
+  <si>
+    <t>OD | GT | 610 TIENDA CAYALA</t>
+  </si>
+  <si>
+    <t>OD | GT | 608 TIENDA SAN CRISTOBAL</t>
   </si>
 </sst>
 </file>
@@ -218,11 +218,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,7 +558,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B02855FB-DB11-4983-8081-D6EA060D646C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -567,17 +567,18 @@
     <col min="5" max="5" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -592,10 +593,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>601</v>
       </c>
@@ -603,7 +604,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1">
         <v>15</v>
@@ -621,15 +622,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>602</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1">
         <v>15</v>
@@ -641,21 +642,21 @@
         <v>85</v>
       </c>
       <c r="G3" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>603</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1">
         <v>15</v>
@@ -670,18 +671,18 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>605</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D5" s="1">
         <v>15</v>
@@ -693,21 +694,21 @@
         <v>91</v>
       </c>
       <c r="G5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>606</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1">
         <v>15</v>
@@ -722,18 +723,18 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>607</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1">
         <v>15</v>
@@ -745,21 +746,21 @@
         <v>97</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>608</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1">
         <v>15</v>
@@ -771,21 +772,21 @@
         <v>100</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>609</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1">
         <v>15</v>
@@ -800,18 +801,18 @@
         <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>610</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D10" s="1">
         <v>15</v>
@@ -823,21 +824,21 @@
         <v>106</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>641</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1">
         <v>16</v>
@@ -849,21 +850,21 @@
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>642</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1">
         <v>16</v>
@@ -875,21 +876,21 @@
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>10642</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D13" s="1">
         <v>16</v>
@@ -901,21 +902,21 @@
         <v>122</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>643</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D14" s="1">
         <v>16</v>
@@ -927,21 +928,21 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>651</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D15" s="1">
         <v>17</v>
@@ -953,10 +954,10 @@
         <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -964,10 +965,10 @@
         <v>652</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D16" s="1">
         <v>17</v>
@@ -979,30 +980,30 @@
         <v>72</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>653</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D17" s="1">
         <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1010,30 +1011,30 @@
         <v>654</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D18" s="1">
         <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>620</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D19" s="1">
         <v>18</v>
@@ -1045,21 +1046,21 @@
         <v>43</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>621</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D20" s="1">
         <v>18</v>
@@ -1071,21 +1072,21 @@
         <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>622</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D21" s="1">
         <v>18</v>
@@ -1097,21 +1098,21 @@
         <v>49</v>
       </c>
       <c r="G21" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>623</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D22" s="1">
         <v>18</v>
@@ -1123,21 +1124,21 @@
         <v>52</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>624</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D23" s="1">
         <v>18</v>
@@ -1149,21 +1150,21 @@
         <v>55</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>625</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D24" s="1">
         <v>18</v>
@@ -1175,21 +1176,21 @@
         <v>58</v>
       </c>
       <c r="G24" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>626</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D25" s="1">
         <v>18</v>
@@ -1201,21 +1202,21 @@
         <v>61</v>
       </c>
       <c r="G25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>627</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D26" s="1">
         <v>18</v>
@@ -1227,10 +1228,10 @@
         <v>64</v>
       </c>
       <c r="G26" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1238,10 +1239,10 @@
         <v>671</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D27" s="1">
         <v>19</v>
@@ -1253,10 +1254,10 @@
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H27" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1264,19 +1265,19 @@
         <v>673</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D28" s="1">
         <v>19</v>
       </c>
       <c r="G28" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H28" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1284,10 +1285,10 @@
         <v>674</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D29" s="1">
         <v>19</v>
@@ -1299,10 +1300,10 @@
         <v>32</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H29" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1310,10 +1311,10 @@
         <v>675</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D30" s="1">
         <v>19</v>
@@ -1325,10 +1326,10 @@
         <v>35</v>
       </c>
       <c r="G30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1336,10 +1337,10 @@
         <v>690</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D31" s="1">
         <v>19</v>
@@ -1351,23 +1352,14 @@
         <v>38</v>
       </c>
       <c r="G31" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H31" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H31" xr:uid="{B02855FB-DB11-4983-8081-D6EA060D646C}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="OD | HN | 652 TIENDA TEGUCIGALPA"/>
-        <filter val="OD | PA | 671 EL DORADO"/>
-        <filter val="OD | PA | 674 VIA BRASIL"/>
-        <filter val="OD | PA | 675 BRISAS DEL GOLF"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H31" xr:uid="{B02855FB-DB11-4983-8081-D6EA060D646C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>